--- a/exports/trend_1d/MOTILALOFS_full_report.xlsx
+++ b/exports/trend_1d/MOTILALOFS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>11.13</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42073</v>
+        <v>42074</v>
       </c>
       <c r="H2" t="n">
-        <v>73.8</v>
+        <v>71.7</v>
       </c>
       <c r="I2" t="n">
         <v>71.87465766426598</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K2" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>16.68</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42100</v>
+        <v>42101</v>
       </c>
       <c r="H3" t="n">
-        <v>77.7</v>
+        <v>78.8</v>
       </c>
       <c r="I3" t="n">
         <v>78.58475405260039</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
-        <v>-8.369999999999999</v>
+        <v>-9.9</v>
       </c>
       <c r="L3" t="n">
         <v>12.83</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>14.42</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42117</v>
+        <v>42118</v>
       </c>
       <c r="H4" t="n">
-        <v>73.5</v>
+        <v>66.25</v>
       </c>
       <c r="I4" t="n">
         <v>68.81293174851005</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.73</v>
+        <v>-15.93</v>
       </c>
       <c r="L4" t="n">
-        <v>8.949999999999999</v>
+        <v>24.62</v>
       </c>
       <c r="M4" t="n">
         <v>1.26</v>
       </c>
       <c r="N4" t="n">
-        <v>1.64</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1.42</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>21.59</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42152</v>
+        <v>42153</v>
       </c>
       <c r="H5" t="n">
-        <v>73.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>80.55520555279847</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.49</v>
+        <v>-21.66</v>
       </c>
       <c r="L5" t="n">
-        <v>20.15</v>
+        <v>24.53</v>
       </c>
       <c r="M5" t="n">
         <v>3.02</v>
       </c>
       <c r="N5" t="n">
-        <v>4.45</v>
+        <v>10.11</v>
       </c>
       <c r="O5" t="n">
         <v>-9.859999999999999</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>18.86</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42235</v>
+        <v>42236</v>
       </c>
       <c r="H6" t="n">
-        <v>81</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>79.64205666351063</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>-1.86</v>
       </c>
       <c r="L6" t="n">
         <v>12.53</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>13.14</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42296</v>
+        <v>42297</v>
       </c>
       <c r="H7" t="n">
-        <v>72.09999999999999</v>
+        <v>81.75</v>
       </c>
       <c r="I7" t="n">
         <v>79.92737140694626</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K7" t="n">
-        <v>8.85</v>
+        <v>-3.35</v>
       </c>
       <c r="L7" t="n">
-        <v>7.96</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>3.24</v>
+        <v>4.37</v>
       </c>
       <c r="N7" t="n">
-        <v>5.08</v>
+        <v>13.38</v>
       </c>
       <c r="O7" t="n">
         <v>-2.35</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>16.94</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42383</v>
+        <v>42384</v>
       </c>
       <c r="H8" t="n">
-        <v>80.05</v>
+        <v>75.8</v>
       </c>
       <c r="I8" t="n">
         <v>79.00796492371711</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.08</v>
+        <v>-7.28</v>
       </c>
       <c r="L8" t="n">
         <v>9.48</v>
@@ -897,7 +992,7 @@
         <v>2.83</v>
       </c>
       <c r="N8" t="n">
-        <v>3.44</v>
+        <v>5.31</v>
       </c>
       <c r="O8" t="n">
         <v>13.38</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>14.57</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42509</v>
+        <v>42510</v>
       </c>
       <c r="H9" t="n">
-        <v>74.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>75.34907737447227</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K9" t="n">
-        <v>1.98</v>
+        <v>-0.79</v>
       </c>
       <c r="L9" t="n">
         <v>7.12</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>12.56</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42676</v>
+        <v>42677</v>
       </c>
       <c r="H10" t="n">
-        <v>138.5</v>
+        <v>133.45</v>
       </c>
       <c r="I10" t="n">
         <v>136.913740075391</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K10" t="n">
-        <v>81.28</v>
+        <v>74.67</v>
       </c>
       <c r="L10" t="n">
         <v>4.58</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>19.08</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42759</v>
+        <v>42760</v>
       </c>
       <c r="H11" t="n">
-        <v>134.1</v>
+        <v>141.45</v>
       </c>
       <c r="I11" t="n">
         <v>140.7434862956067</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.49</v>
+        <v>-5.99</v>
       </c>
       <c r="L11" t="n">
         <v>7.12</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.39</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H12" t="n">
-        <v>241.4</v>
+        <v>233.65</v>
       </c>
       <c r="I12" t="n">
         <v>237.3276729152813</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K12" t="n">
-        <v>70.66</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="L12" t="n">
         <v>5.97</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>21.54</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42895</v>
+        <v>42898</v>
       </c>
       <c r="H13" t="n">
-        <v>281.5</v>
+        <v>286.9</v>
       </c>
       <c r="I13" t="n">
         <v>283.9819538002839</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K13" t="n">
-        <v>-20.48</v>
+        <v>-22.79</v>
       </c>
       <c r="L13" t="n">
-        <v>22.51</v>
+        <v>24.97</v>
       </c>
       <c r="M13" t="n">
         <v>1.34</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>14.01</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42933</v>
+        <v>42934</v>
       </c>
       <c r="H14" t="n">
-        <v>276.5</v>
+        <v>268.95</v>
       </c>
       <c r="I14" t="n">
         <v>272.6708054046162</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.62</v>
+        <v>-6.26</v>
       </c>
       <c r="L14" t="n">
         <v>7.2</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>13.17</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42963</v>
+        <v>42964</v>
       </c>
       <c r="H15" t="n">
-        <v>276.75</v>
+        <v>299</v>
       </c>
       <c r="I15" t="n">
         <v>292.0819078504226</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.9</v>
+        <v>-11.17</v>
       </c>
       <c r="L15" t="n">
-        <v>6.8</v>
+        <v>11.99</v>
       </c>
       <c r="M15" t="n">
         <v>1.24</v>
       </c>
       <c r="N15" t="n">
-        <v>6.81</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="O15" t="n">
         <v>-2.73</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>13.87</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43046</v>
+        <v>43047</v>
       </c>
       <c r="H16" t="n">
-        <v>340.85</v>
+        <v>332.65</v>
       </c>
       <c r="I16" t="n">
         <v>334.3992386681174</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K16" t="n">
-        <v>14</v>
+        <v>11.25</v>
       </c>
       <c r="L16" t="n">
         <v>6.89</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>13.42</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43081</v>
+        <v>43082</v>
       </c>
       <c r="H17" t="n">
-        <v>335</v>
+        <v>345.2</v>
       </c>
       <c r="I17" t="n">
         <v>344.8497071581573</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.71</v>
+        <v>-3.77</v>
       </c>
       <c r="L17" t="n">
         <v>5.97</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.83</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43117</v>
+        <v>43118</v>
       </c>
       <c r="H18" t="n">
-        <v>367.15</v>
+        <v>349.6</v>
       </c>
       <c r="I18" t="n">
         <v>353.0633523030402</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K18" t="n">
-        <v>6.36</v>
+        <v>1.27</v>
       </c>
       <c r="L18" t="n">
         <v>5.76</v>
@@ -1467,7 +1682,7 @@
         <v>0.3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.16</v>
+        <v>4.78</v>
       </c>
       <c r="O18" t="n">
         <v>3.04</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>15.67</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43285</v>
+        <v>43286</v>
       </c>
       <c r="H19" t="n">
-        <v>210.25</v>
+        <v>217.8</v>
       </c>
       <c r="I19" t="n">
         <v>210.9441621890487</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K19" t="n">
-        <v>39.86</v>
+        <v>37.7</v>
       </c>
       <c r="L19" t="n">
         <v>7.52</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>7</v>
+      </c>
+      <c r="U19" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>14.92</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43294</v>
+        <v>43297</v>
       </c>
       <c r="H20" t="n">
-        <v>200</v>
+        <v>193.55</v>
       </c>
       <c r="I20" t="n">
         <v>194.6695493418808</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K20" t="n">
-        <v>-8.17</v>
+        <v>-11.13</v>
       </c>
       <c r="L20" t="n">
-        <v>8.720000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="M20" t="n">
         <v>0.6899999999999999</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>15.2</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43307</v>
+        <v>43308</v>
       </c>
       <c r="H21" t="n">
-        <v>210.4</v>
+        <v>226.5</v>
       </c>
       <c r="I21" t="n">
         <v>219.2655633994839</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K21" t="n">
-        <v>-8.710000000000001</v>
+        <v>-17.02</v>
       </c>
       <c r="L21" t="n">
-        <v>12.12</v>
+        <v>20.1</v>
       </c>
       <c r="M21" t="n">
         <v>0.71</v>
       </c>
       <c r="N21" t="n">
-        <v>3.43</v>
+        <v>7.65</v>
       </c>
       <c r="O21" t="n">
         <v>-3.22</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>14.47</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H22" t="n">
-        <v>209.65</v>
+        <v>204.1</v>
       </c>
       <c r="I22" t="n">
         <v>205.0448122886628</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K22" t="n">
-        <v>-7.44</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>10.18</v>
+        <v>10.2</v>
       </c>
       <c r="M22" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="N22" t="n">
         <v>2.8</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>12.79</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43405</v>
+        <v>43406</v>
       </c>
       <c r="H23" t="n">
-        <v>165.25</v>
+        <v>171.3</v>
       </c>
       <c r="I23" t="n">
         <v>165.6276794154856</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K23" t="n">
-        <v>19.03</v>
+        <v>16.07</v>
       </c>
       <c r="L23" t="n">
         <v>3.53</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>17.3</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43497</v>
+        <v>43500</v>
       </c>
       <c r="H24" t="n">
-        <v>157.45</v>
+        <v>155.5</v>
       </c>
       <c r="I24" t="n">
         <v>157.1439321577297</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K24" t="n">
-        <v>-8.09</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="L24" t="n">
         <v>14.19</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>10.9</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43542</v>
+        <v>43543</v>
       </c>
       <c r="H25" t="n">
-        <v>157.55</v>
+        <v>159.7</v>
       </c>
       <c r="I25" t="n">
         <v>157.5713221403448</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.32</v>
+        <v>-2.7</v>
       </c>
       <c r="L25" t="n">
-        <v>3.28</v>
+        <v>4.12</v>
       </c>
       <c r="M25" t="n">
         <v>6.36</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43628</v>
+        <v>43629</v>
       </c>
       <c r="H26" t="n">
-        <v>179.95</v>
+        <v>177.2</v>
       </c>
       <c r="I26" t="n">
         <v>179.6922666125405</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K26" t="n">
-        <v>12.68</v>
+        <v>10.96</v>
       </c>
       <c r="L26" t="n">
         <v>7.64</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>13.71</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43703</v>
+        <v>43704</v>
       </c>
       <c r="H27" t="n">
-        <v>141.4</v>
+        <v>149</v>
       </c>
       <c r="I27" t="n">
         <v>145.6212815182408</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K27" t="n">
-        <v>20.2</v>
+        <v>15.91</v>
       </c>
       <c r="L27" t="n">
         <v>2.26</v>
@@ -1980,7 +2303,7 @@
         <v>2.48</v>
       </c>
       <c r="N27" t="n">
-        <v>5.02</v>
+        <v>5.37</v>
       </c>
       <c r="O27" t="n">
         <v>-1.53</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>15.38</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43745</v>
+        <v>43747</v>
       </c>
       <c r="H28" t="n">
-        <v>152.5</v>
+        <v>147.2</v>
       </c>
       <c r="I28" t="n">
         <v>148.4914891759392</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K28" t="n">
-        <v>2.35</v>
+        <v>-1.21</v>
       </c>
       <c r="L28" t="n">
         <v>8.890000000000001</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>20.2</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43769</v>
+        <v>43770</v>
       </c>
       <c r="H29" t="n">
-        <v>155.25</v>
+        <v>173</v>
       </c>
       <c r="I29" t="n">
         <v>172.7449367530572</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.47</v>
+        <v>-17.53</v>
       </c>
       <c r="L29" t="n">
-        <v>13.45</v>
+        <v>20.18</v>
       </c>
       <c r="M29" t="n">
-        <v>1.54</v>
+        <v>4.83</v>
       </c>
       <c r="N29" t="n">
-        <v>8</v>
+        <v>11.43</v>
       </c>
       <c r="O29" t="n">
         <v>-3.48</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>18.11</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H30" t="n">
-        <v>194.95</v>
+        <v>186.15</v>
       </c>
       <c r="I30" t="n">
         <v>193.1070036523247</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K30" t="n">
-        <v>12.69</v>
+        <v>7.6</v>
       </c>
       <c r="L30" t="n">
         <v>7.2</v>
       </c>
       <c r="M30" t="n">
-        <v>2.4</v>
+        <v>3.82</v>
       </c>
       <c r="N30" t="n">
         <v>4.93</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>12.83</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43987</v>
+        <v>43990</v>
       </c>
       <c r="H31" t="n">
-        <v>141.55</v>
+        <v>144.8</v>
       </c>
       <c r="I31" t="n">
         <v>143.3143631970007</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K31" t="n">
-        <v>23.96</v>
+        <v>22.21</v>
       </c>
       <c r="L31" t="n">
         <v>4.06</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>12.72</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44082</v>
+        <v>44083</v>
       </c>
       <c r="H32" t="n">
-        <v>163.8</v>
+        <v>161.85</v>
       </c>
       <c r="I32" t="n">
         <v>163.3001740733339</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K32" t="n">
-        <v>13.12</v>
+        <v>11.77</v>
       </c>
       <c r="L32" t="n">
         <v>9.98</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>10.18</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44149</v>
+        <v>44152</v>
       </c>
       <c r="H33" t="n">
-        <v>145.65</v>
+        <v>156</v>
       </c>
       <c r="I33" t="n">
         <v>151.3069818876518</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K33" t="n">
-        <v>10.01</v>
+        <v>3.61</v>
       </c>
       <c r="L33" t="n">
         <v>3.43</v>
@@ -2322,7 +2717,7 @@
         <v>3.83</v>
       </c>
       <c r="N33" t="n">
-        <v>4.73</v>
+        <v>7.11</v>
       </c>
       <c r="O33" t="n">
         <v>-1.19</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>13.65</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44299</v>
+        <v>44301</v>
       </c>
       <c r="H34" t="n">
-        <v>153.4</v>
+        <v>151.55</v>
       </c>
       <c r="I34" t="n">
         <v>153.1972102072515</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.67</v>
+        <v>-2.85</v>
       </c>
       <c r="L34" t="n">
         <v>7.05</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>11.54</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44320</v>
+        <v>44321</v>
       </c>
       <c r="H35" t="n">
-        <v>160.7</v>
+        <v>164.9</v>
       </c>
       <c r="I35" t="n">
         <v>163.0364188332068</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.04</v>
+        <v>-8.81</v>
       </c>
       <c r="L35" t="n">
         <v>11.18</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>11.64</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44406</v>
+        <v>44407</v>
       </c>
       <c r="H36" t="n">
-        <v>264.75</v>
+        <v>235.8</v>
       </c>
       <c r="I36" t="n">
         <v>237.7898590647298</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K36" t="n">
-        <v>60.55</v>
+        <v>43</v>
       </c>
       <c r="L36" t="n">
         <v>2.37</v>
       </c>
       <c r="M36" t="n">
-        <v>2.83</v>
+        <v>7.46</v>
       </c>
       <c r="N36" t="n">
-        <v>4.04</v>
+        <v>10.93</v>
       </c>
       <c r="O36" t="n">
         <v>2.61</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>23</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44461</v>
+        <v>44462</v>
       </c>
       <c r="H37" t="n">
-        <v>209.95</v>
+        <v>218.35</v>
       </c>
       <c r="I37" t="n">
         <v>217.415450290198</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K37" t="n">
-        <v>10.96</v>
+        <v>7.4</v>
       </c>
       <c r="L37" t="n">
         <v>6.85</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>12.47</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44588</v>
+        <v>44589</v>
       </c>
       <c r="H38" t="n">
-        <v>224.4</v>
+        <v>215.05</v>
       </c>
       <c r="I38" t="n">
         <v>222.1188593530975</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K38" t="n">
-        <v>2.77</v>
+        <v>-1.51</v>
       </c>
       <c r="L38" t="n">
         <v>4.88</v>
       </c>
       <c r="M38" t="n">
-        <v>1.33</v>
+        <v>6.42</v>
       </c>
       <c r="N38" t="n">
         <v>4.7</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>6</v>
+      </c>
+      <c r="U38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>12.3</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44645</v>
+        <v>44648</v>
       </c>
       <c r="H39" t="n">
-        <v>228.6</v>
+        <v>233.75</v>
       </c>
       <c r="I39" t="n">
         <v>229.9810641742359</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.3</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="L39" t="n">
         <v>11.58</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>12.74</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44692</v>
+        <v>44693</v>
       </c>
       <c r="H40" t="n">
-        <v>213.35</v>
+        <v>201.05</v>
       </c>
       <c r="I40" t="n">
         <v>207.4297118377241</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K40" t="n">
-        <v>-8.73</v>
+        <v>-13.99</v>
       </c>
       <c r="L40" t="n">
-        <v>10.97</v>
+        <v>14.27</v>
       </c>
       <c r="M40" t="n">
         <v>2.41</v>
       </c>
       <c r="N40" t="n">
-        <v>5.53</v>
+        <v>5.77</v>
       </c>
       <c r="O40" t="n">
         <v>2.25</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>16.06</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44816</v>
+        <v>44817</v>
       </c>
       <c r="H41" t="n">
-        <v>192.9</v>
+        <v>202.75</v>
       </c>
       <c r="I41" t="n">
         <v>202.6628996407844</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K41" t="n">
-        <v>4.05</v>
+        <v>-0.85</v>
       </c>
       <c r="L41" t="n">
         <v>9.720000000000001</v>
@@ -2778,7 +3269,7 @@
         <v>2.47</v>
       </c>
       <c r="N41" t="n">
-        <v>4.57</v>
+        <v>5.11</v>
       </c>
       <c r="O41" t="n">
         <v>-5.77</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>5</v>
+      </c>
+      <c r="U41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>8.49</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H42" t="n">
-        <v>187.85</v>
+        <v>185.5</v>
       </c>
       <c r="I42" t="n">
         <v>186.4993151673734</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K42" t="n">
-        <v>-7.35</v>
+        <v>-8.51</v>
       </c>
       <c r="L42" t="n">
-        <v>8.460000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="M42" t="n">
         <v>2.22</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.57</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44909</v>
+        <v>44910</v>
       </c>
       <c r="H43" t="n">
-        <v>169.1</v>
+        <v>177.1</v>
       </c>
       <c r="I43" t="n">
         <v>173.0501322827315</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K43" t="n">
-        <v>8.84</v>
+        <v>4.53</v>
       </c>
       <c r="L43" t="n">
         <v>1</v>
@@ -2892,7 +3407,7 @@
         <v>1.96</v>
       </c>
       <c r="N43" t="n">
-        <v>3.94</v>
+        <v>4.73</v>
       </c>
       <c r="O43" t="n">
         <v>-1.25</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>7.59</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44951</v>
+        <v>44953</v>
       </c>
       <c r="H44" t="n">
-        <v>173.1</v>
+        <v>170.3</v>
       </c>
       <c r="I44" t="n">
         <v>172.1275334101209</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.26</v>
+        <v>-3.84</v>
       </c>
       <c r="L44" t="n">
         <v>5.42</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>10.29</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45014</v>
+        <v>45016</v>
       </c>
       <c r="H45" t="n">
-        <v>145.05</v>
+        <v>152.6</v>
       </c>
       <c r="I45" t="n">
         <v>152.2083466647293</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K45" t="n">
-        <v>14.83</v>
+        <v>10.39</v>
       </c>
       <c r="L45" t="n">
         <v>3.2</v>
@@ -3006,7 +3545,7 @@
         <v>13</v>
       </c>
       <c r="N45" t="n">
-        <v>3.62</v>
+        <v>5.21</v>
       </c>
       <c r="O45" t="n">
         <v>-1.62</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>11.45</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45051</v>
+        <v>45054</v>
       </c>
       <c r="H46" t="n">
-        <v>150.35</v>
+        <v>146.15</v>
       </c>
       <c r="I46" t="n">
         <v>146.4823595547522</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.47</v>
+        <v>-4.23</v>
       </c>
       <c r="L46" t="n">
-        <v>4.16</v>
+        <v>4.52</v>
       </c>
       <c r="M46" t="n">
         <v>2.65</v>
       </c>
       <c r="N46" t="n">
-        <v>1.96</v>
+        <v>2.79</v>
       </c>
       <c r="O46" t="n">
         <v>5.21</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>10.93</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45056</v>
+        <v>45057</v>
       </c>
       <c r="H47" t="n">
-        <v>158.4</v>
+        <v>165.05</v>
       </c>
       <c r="I47" t="n">
         <v>162.1200787188546</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.380000000000001</v>
+        <v>-12.93</v>
       </c>
       <c r="L47" t="n">
-        <v>8.619999999999999</v>
+        <v>13.55</v>
       </c>
       <c r="M47" t="n">
         <v>1.3</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>11.8</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="H48" t="n">
-        <v>407.3</v>
+        <v>395</v>
       </c>
       <c r="I48" t="n">
         <v>400.3626617635153</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K48" t="n">
-        <v>146.77</v>
+        <v>139.32</v>
       </c>
       <c r="L48" t="n">
         <v>6.73</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>208</v>
+        <v>209</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>11</v>
+      </c>
+      <c r="U48" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>16.49</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H49" t="n">
-        <v>416.7</v>
+        <v>438.2</v>
       </c>
       <c r="I49" t="n">
         <v>428.4781765536945</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.49</v>
+        <v>-10.94</v>
       </c>
       <c r="L49" t="n">
-        <v>7.67</v>
+        <v>12.28</v>
       </c>
       <c r="M49" t="n">
         <v>1.12</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>14.97</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H50" t="n">
-        <v>586.5</v>
+        <v>537.8</v>
       </c>
       <c r="I50" t="n">
         <v>548.5112406829251</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K50" t="n">
-        <v>33.84</v>
+        <v>22.73</v>
       </c>
       <c r="L50" t="n">
         <v>4.08</v>
@@ -3291,7 +3890,7 @@
         <v>1.95</v>
       </c>
       <c r="N50" t="n">
-        <v>4.71</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O50" t="n">
         <v>5.16</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>21.13</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45450</v>
+        <v>45453</v>
       </c>
       <c r="H51" t="n">
-        <v>606.7</v>
+        <v>656.1</v>
       </c>
       <c r="I51" t="n">
         <v>627.1585149057246</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K51" t="n">
-        <v>-12.81</v>
+        <v>-22</v>
       </c>
       <c r="L51" t="n">
-        <v>13.89</v>
+        <v>34.25</v>
       </c>
       <c r="M51" t="n">
-        <v>5.33</v>
+        <v>7.97</v>
       </c>
       <c r="N51" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="O51" t="n">
         <v>-8.300000000000001</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>15.9</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45471</v>
+        <v>45474</v>
       </c>
       <c r="H52" t="n">
-        <v>614.55</v>
+        <v>591.5</v>
       </c>
       <c r="I52" t="n">
         <v>592.3947156309323</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K52" t="n">
-        <v>-6.33</v>
+        <v>-9.85</v>
       </c>
       <c r="L52" t="n">
-        <v>7.48</v>
+        <v>11.6</v>
       </c>
       <c r="M52" t="n">
         <v>3.89</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>16.87</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45499</v>
+        <v>45502</v>
       </c>
       <c r="H53" t="n">
-        <v>590.75</v>
+        <v>606.7</v>
       </c>
       <c r="I53" t="n">
         <v>590.815924434579</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K53" t="n">
-        <v>0.13</v>
+        <v>-2.57</v>
       </c>
       <c r="L53" t="n">
         <v>3.9</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>13.11</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H54" t="n">
-        <v>727.25</v>
+        <v>703.9</v>
       </c>
       <c r="I54" t="n">
         <v>705.0427865314799</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K54" t="n">
-        <v>19.87</v>
+        <v>16.02</v>
       </c>
       <c r="L54" t="n">
         <v>4.73</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>17.44</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45576</v>
+        <v>45579</v>
       </c>
       <c r="H55" t="n">
-        <v>808.55</v>
+        <v>826.8</v>
       </c>
       <c r="I55" t="n">
         <v>826.6260255519531</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K55" t="n">
-        <v>-14.87</v>
+        <v>-17.46</v>
       </c>
       <c r="L55" t="n">
-        <v>15.56</v>
+        <v>18.2</v>
       </c>
       <c r="M55" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="N55" t="n">
         <v>6.8</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>13.98</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H56" t="n">
-        <v>901.2</v>
+        <v>878.1</v>
       </c>
       <c r="I56" t="n">
         <v>888.0131257808728</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K56" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="L56" t="n">
         <v>2.48</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>15.87</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45763</v>
+        <v>45764</v>
       </c>
       <c r="H57" t="n">
-        <v>639.35</v>
+        <v>653.35</v>
       </c>
       <c r="I57" t="n">
         <v>641.2495061781145</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K57" t="n">
-        <v>27.19</v>
+        <v>25.6</v>
       </c>
       <c r="L57" t="n">
         <v>4.42</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>4</v>
+      </c>
+      <c r="U57" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>14.84</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45776</v>
+        <v>45777</v>
       </c>
       <c r="H58" t="n">
-        <v>673.9</v>
+        <v>652.75</v>
       </c>
       <c r="I58" t="n">
         <v>666.3008795204347</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K58" t="n">
-        <v>3.15</v>
+        <v>-0.09</v>
       </c>
       <c r="L58" t="n">
         <v>3.3</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>17.57</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45791</v>
+        <v>45792</v>
       </c>
       <c r="H59" t="n">
-        <v>739.55</v>
+        <v>760.3</v>
       </c>
       <c r="I59" t="n">
         <v>748.7178271519786</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K59" t="n">
-        <v>-13.3</v>
+        <v>-16.48</v>
       </c>
       <c r="L59" t="n">
-        <v>13.98</v>
+        <v>17.27</v>
       </c>
       <c r="M59" t="n">
         <v>2.99</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>15.62</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45897</v>
+        <v>45898</v>
       </c>
       <c r="H60" t="n">
-        <v>889</v>
+        <v>857.3</v>
       </c>
       <c r="I60" t="n">
         <v>885.4678022669247</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K60" t="n">
-        <v>16.93</v>
+        <v>12.76</v>
       </c>
       <c r="L60" t="n">
         <v>3.66</v>
@@ -3861,7 +4580,7 @@
         <v>2.56</v>
       </c>
       <c r="N60" t="n">
-        <v>3.18</v>
+        <v>3.57</v>
       </c>
       <c r="O60" t="n">
         <v>2.81</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>11.79</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="H61" t="n">
-        <v>950.3</v>
+        <v>958.35</v>
       </c>
       <c r="I61" t="n">
         <v>952.8147891757187</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K61" t="n">
-        <v>-10.85</v>
+        <v>-11.79</v>
       </c>
       <c r="L61" t="n">
         <v>12.21</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>8.35</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="H62" t="n">
-        <v>1025.3</v>
+        <v>978</v>
       </c>
       <c r="I62" t="n">
         <v>998.5471885169802</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K62" t="n">
-        <v>6.99</v>
+        <v>2.05</v>
       </c>
       <c r="L62" t="n">
         <v>8.42</v>
       </c>
       <c r="M62" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="N62" t="n">
         <v>7.65</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>10.74</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H63" t="n">
-        <v>698.85</v>
+        <v>757.4</v>
       </c>
       <c r="I63" t="n">
         <v>719.4331559071089</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K63" t="n">
-        <v>28.54</v>
+        <v>22.56</v>
       </c>
       <c r="L63" t="n">
         <v>4.6</v>
@@ -4032,7 +4787,7 @@
         <v>7.34</v>
       </c>
       <c r="N63" t="n">
-        <v>7.93</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="O63" t="n">
         <v>-4.61</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>6</v>
+      </c>
+      <c r="U63" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>16.01</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="H64" t="n">
-        <v>940.25</v>
+        <v>871.95</v>
       </c>
       <c r="I64" t="n">
         <v>895.1129173464146</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K64" t="n">
-        <v>24.14</v>
+        <v>15.12</v>
       </c>
       <c r="L64" t="n">
         <v>4.62</v>
@@ -4089,7 +4856,7 @@
         <v>2.38</v>
       </c>
       <c r="N64" t="n">
-        <v>4.35</v>
+        <v>7.26</v>
       </c>
       <c r="O64" t="n">
         <v>8.380000000000001</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>13.97</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="H65" t="n">
-        <v>903.7</v>
+        <v>955</v>
       </c>
       <c r="I65" t="n">
         <v>934.6500222142037</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.64</v>
+        <v>-9.52</v>
       </c>
       <c r="L65" t="n">
-        <v>8.32</v>
+        <v>10.56</v>
       </c>
       <c r="M65" t="n">
         <v>1.06</v>
       </c>
       <c r="N65" t="n">
-        <v>2.21</v>
+        <v>5.68</v>
       </c>
       <c r="O65" t="n">
         <v>-7.26</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>11.23</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="H66" t="n">
-        <v>977</v>
+        <v>925.8</v>
       </c>
       <c r="I66" t="n">
         <v>974.5371819033485</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K66" t="n">
-        <v>2.3</v>
+        <v>-3.06</v>
       </c>
       <c r="L66" t="n">
         <v>6.06</v>
@@ -4203,7 +4994,7 @@
         <v>1.57</v>
       </c>
       <c r="N66" t="n">
-        <v>5.02</v>
+        <v>5.24</v>
       </c>
       <c r="O66" t="n">
         <v>5.68</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,14 @@
       <c r="Q67" t="n">
         <v>4</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9221,7 +10032,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64.59999999999999</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -9231,7 +10042,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -9241,7 +10052,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8">
@@ -9251,7 +10062,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -9261,7 +10072,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -9271,7 +10082,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>124.2</v>
+        <v>125.2</v>
       </c>
     </row>
     <row r="11">
@@ -9281,7 +10092,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -9291,7 +10102,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -9301,7 +10112,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29.2</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="14">
@@ -9311,7 +10122,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.57</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="15">
@@ -9321,7 +10132,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14.51</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="16">
@@ -9331,7 +10142,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.43</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="17">
@@ -9341,7 +10152,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>146.77</v>
+        <v>139.32</v>
       </c>
     </row>
     <row r="18">
@@ -9351,7 +10162,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.8</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="19">
@@ -9361,7 +10172,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.74</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="20">
@@ -9371,7 +10182,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.12</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="21">
@@ -9381,7 +10192,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.51</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="22">
@@ -9401,7 +10212,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
@@ -9411,7 +10222,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="25">
@@ -9431,7 +10242,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.4</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="27">
@@ -9451,7 +10262,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
